--- a/data/trans_dic/P19C11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,43</t>
+          <t>3,33; 6,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,02</t>
+          <t>2,91; 5,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,3</t>
+          <t>3,43; 5,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,23</t>
+          <t>1,49; 4,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,25</t>
+          <t>3,11; 5,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,27</t>
+          <t>2,28; 4,33</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,73</t>
+          <t>3,46; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,08</t>
+          <t>1,64; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,24</t>
+          <t>2,58; 5,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,65</t>
+          <t>3,82; 6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,2</t>
+          <t>3,05; 5,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,37</t>
+          <t>3,66; 5,41</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,03</t>
+          <t>3,15; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,49</t>
+          <t>3,14; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,54</t>
+          <t>3,46; 4,53</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20254; 39333</t>
+          <t>20375; 40049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19429; 32683</t>
+          <t>18951; 32640</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43376; 66900</t>
+          <t>43355; 67147</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16498; 49300</t>
+          <t>17390; 50898</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29513; 49428</t>
+          <t>29321; 49026</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48482; 90053</t>
+          <t>48052; 91387</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23192; 46219</t>
+          <t>23721; 46033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15442; 46818</t>
+          <t>15138; 48252</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40714; 84276</t>
+          <t>41442; 84298</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34748; 59137</t>
+          <t>34024; 58656</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32268; 55271</t>
+          <t>32423; 55095</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72742; 104919</t>
+          <t>71425; 105713</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>111338; 168678</t>
+          <t>105752; 163532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113688; 160699</t>
+          <t>112396; 161142</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>236545; 314939</t>
+          <t>239540; 314375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Habitat-trans_dic.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,55</t>
+          <t>3,14; 6,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,01</t>
+          <t>3,02; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,32</t>
+          <t>3,4; 5,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,36</t>
+          <t>2,52; 4,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,2</t>
+          <t>2,96; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,33</t>
+          <t>3,05; 4,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,71</t>
+          <t>3,83; 7,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,23</t>
+          <t>3,8; 6,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,24</t>
+          <t>4,09; 6,3</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,59</t>
+          <t>3,78; 6,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,18</t>
+          <t>3,32; 5,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,41</t>
+          <t>3,84; 5,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,88</t>
+          <t>3,94; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,5</t>
+          <t>3,71; 4,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,53</t>
+          <t>3,98; 4,86</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53921</t>
+          <t>58334</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20375; 40049</t>
+          <t>20727; 41110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18951; 32640</t>
+          <t>21343; 37418</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43355; 67147</t>
+          <t>46389; 71479</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33572</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38086</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>76766</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17390; 50898</t>
+          <t>25631; 49588</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29321; 49026</t>
+          <t>31012; 51391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48052; 91387</t>
+          <t>62849; 96503</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33281</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>80816</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23721; 46033</t>
+          <t>29614; 57395</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15138; 48252</t>
+          <t>30192; 51879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41442; 84298</t>
+          <t>64196; 98889</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87803</t>
+          <t>91489</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34024; 58656</t>
+          <t>35874; 60609</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32423; 55095</t>
+          <t>35693; 57034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71425; 105713</t>
+          <t>77761; 108945</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>105752; 163532</t>
+          <t>133792; 180390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>112396; 161142</t>
+          <t>134476; 173205</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239540; 314375</t>
+          <t>279706; 341573</t>
         </is>
       </c>
     </row>
